--- a/data/trans_orig/IP11A-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP11A-Provincia-trans_orig.xlsx
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>690</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>4965</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1359</t>
+          <t>760</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5950</t>
+          <t>5860</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>48,3%</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>3221</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>609</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5472</t>
+          <t>5279</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>43,51%</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4405</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>690</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5318</t>
+          <t>5422</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>44,69%</t>
         </is>
       </c>
     </row>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>786</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5339</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7214</t>
+          <t>7298</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1496,12 +1496,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>60,15%</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>3075</t>
+          <t>3088</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>82,14%</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2587</t>
+          <t>2586</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>68,79%</t>
         </is>
       </c>
     </row>
@@ -2389,12 +2389,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>580</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>3759</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3785</t>
+          <t>3719</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4390</t>
+          <t>4740</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>40,15%</t>
         </is>
       </c>
     </row>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2556</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>624</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4332</t>
+          <t>4349</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3051,12 +3051,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>5671</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>48,04%</t>
         </is>
       </c>
     </row>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2935</t>
+          <t>2943</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3862</t>
+          <t>3274</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>623</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4727</t>
+          <t>4726</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3227,12 +3227,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>682</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4815</t>
+          <t>4323</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>649</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4432</t>
+          <t>4608</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3277,12 +3277,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2587</t>
+          <t>2694</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7990</t>
+          <t>8412</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3312,12 +3312,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>71,25%</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2346</t>
+          <t>3089</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3744</t>
+          <t>3196</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4114</t>
+          <t>4009</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,04%</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3128</t>
+          <t>3435</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,7 +3929,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3726</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,7 +3964,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,12 +3979,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>577</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4776</t>
+          <t>5474</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>36,91%</t>
         </is>
       </c>
     </row>
@@ -4057,12 +4057,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>1203</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>5270</t>
+          <t>5380</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>677</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>6117</t>
+          <t>5718</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>38,56%</t>
         </is>
       </c>
     </row>
@@ -4135,12 +4135,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3143</t>
+          <t>2773</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>6335</t>
+          <t>6324</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4150,12 +4150,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5490</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>5138</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>11205</t>
+          <t>11119</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>74,98%</t>
         </is>
       </c>
     </row>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2514</t>
+          <t>2790</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4779,7 +4779,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>2514</t>
+          <t>2790</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2790</t>
+          <t>2038</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2790</t>
+          <t>2038</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>73,05%</t>
         </is>
       </c>
     </row>
@@ -5765,7 +5765,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3213</t>
+          <t>2933</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>3214</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>70,27%</t>
         </is>
       </c>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>3636</t>
+          <t>3337</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>72,97%</t>
         </is>
       </c>
     </row>
@@ -5986,7 +5986,7 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>280</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6021,12 +6021,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>639</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>3860</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>85,83%</t>
         </is>
       </c>
     </row>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>2648</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>3655</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>19,73%</t>
         </is>
       </c>
     </row>
@@ -6525,7 +6525,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>2723</t>
+          <t>3374</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>49,29%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6555,12 +6555,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>641</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>4757</t>
+          <t>4721</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6590,12 +6590,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>674</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>5435</t>
+          <t>6071</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>32,77%</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2746</t>
+          <t>2771</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6668,12 +6668,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>6293</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1386</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>7545</t>
+          <t>7640</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>41,24%</t>
         </is>
       </c>
     </row>
@@ -6746,12 +6746,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>6177</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6781,12 +6781,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>1323</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>6270</t>
+          <t>6840</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>58,55%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>4199</t>
+          <t>4174</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>11075</t>
+          <t>11093</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>59,87%</t>
         </is>
       </c>
     </row>
@@ -6864,7 +6864,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>3405</t>
+          <t>3413</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>643</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>4948</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>1322</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>6319</t>
+          <t>6973</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>37,64%</t>
         </is>
       </c>
     </row>
@@ -7355,7 +7355,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3275</t>
+          <t>3527</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>3814</t>
+          <t>3640</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7405,7 +7405,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>27,14%</t>
         </is>
       </c>
     </row>
@@ -7428,12 +7428,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>598</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>4076</t>
+          <t>4078</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>1422</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>5987</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7498,12 +7498,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>2777</t>
+          <t>2811</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>8367</t>
+          <t>8439</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>62,93%</t>
         </is>
       </c>
     </row>
@@ -7546,7 +7546,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>3129</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>671</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>4965</t>
+          <t>4841</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7611,12 +7611,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>1192</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>6080</t>
+          <t>6246</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>46,57%</t>
         </is>
       </c>
     </row>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>481</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>4095</t>
+          <t>4146</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7669,12 +7669,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>3106</t>
+          <t>3160</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7724,12 +7724,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>966</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>6030</t>
+          <t>6142</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7739,12 +7739,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>45,8%</t>
         </is>
       </c>
     </row>
@@ -7807,7 +7807,7 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>2587</t>
+          <t>2176</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>2511</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>21,83%</t>
         </is>
       </c>
     </row>
@@ -8258,47 +8258,47 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
+          <t>481</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>4861</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>3,92%</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>10,45%</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t>1826</t>
+        </is>
+      </c>
+      <c r="S70" s="2" t="inlineStr">
+        <is>
           <t>485</t>
         </is>
       </c>
-      <c r="M70" s="2" t="inlineStr">
-        <is>
-          <t>5179</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
-      <c r="O70" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="P70" s="2" t="inlineStr">
-        <is>
-          <t>11,13%</t>
-        </is>
-      </c>
-      <c r="Q70" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R70" s="2" t="inlineStr">
-        <is>
-          <t>1826</t>
-        </is>
-      </c>
-      <c r="S70" s="2" t="inlineStr">
-        <is>
-          <t>481</t>
-        </is>
-      </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -8336,12 +8336,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>4442</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>12043</t>
+          <t>11615</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>4888</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>13705</t>
+          <t>13402</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8386,12 +8386,12 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>10902</t>
+          <t>10624</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>22439</t>
+          <t>22594</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,61%</t>
         </is>
       </c>
     </row>
@@ -8449,12 +8449,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>2418</t>
+          <t>2528</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>9127</t>
+          <t>9333</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>7910</t>
+          <t>8093</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>17715</t>
+          <t>17195</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8499,12 +8499,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>12157</t>
+          <t>12177</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>23490</t>
+          <t>23990</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>29,32%</t>
         </is>
       </c>
     </row>
@@ -8562,49 +8562,49 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>6481</t>
+          <t>6260</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
+          <t>15066</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>29,63%</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>17,73%</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>42,67%</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>9944</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
           <t>15188</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>29,63%</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>18,36%</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>43,02%</t>
-        </is>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>9944</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="inlineStr">
-        <is>
-          <t>6032</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr">
-        <is>
-          <t>15409</t>
-        </is>
-      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>21,37%</t>
@@ -8612,12 +8612,12 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>14554</t>
+          <t>14276</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>27543</t>
+          <t>26818</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -8647,12 +8647,12 @@
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>32,77%</t>
         </is>
       </c>
     </row>
@@ -8675,12 +8675,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>8190</t>
+          <t>8247</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>16834</t>
+          <t>17358</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -8690,12 +8690,12 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>9507</t>
+          <t>9479</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>19199</t>
+          <t>19742</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8745,12 +8745,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>20056</t>
+          <t>20325</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>33319</t>
+          <t>33477</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,91%</t>
         </is>
       </c>
     </row>
@@ -9294,7 +9294,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2793</t>
+          <t>2877</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9309,7 +9309,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9329,7 +9329,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>53,02%</t>
         </is>
       </c>
     </row>
@@ -9520,7 +9520,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3427</t>
+          <t>3799</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9535,7 +9535,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9555,7 +9555,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3435</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9570,7 +9570,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>69,34%</t>
         </is>
       </c>
     </row>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>659</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4629</t>
+          <t>4535</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9643,12 +9643,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9663,12 +9663,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>651</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4608</t>
+          <t>4634</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9678,12 +9678,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,9%</t>
         </is>
       </c>
     </row>
@@ -9859,7 +9859,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2784</t>
+          <t>2749</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9874,7 +9874,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9894,7 +9894,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3258</t>
+          <t>2994</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9909,7 +9909,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>52,91%</t>
         </is>
       </c>
     </row>
@@ -10202,7 +10202,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5386</t>
+          <t>5085</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10217,7 +10217,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10237,7 +10237,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6003</t>
+          <t>5735</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>28,88%</t>
         </is>
       </c>
     </row>
@@ -10315,7 +10315,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3267</t>
+          <t>2685</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10330,7 +10330,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10350,7 +10350,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2755</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10365,7 +10365,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>15,94%</t>
         </is>
       </c>
     </row>
@@ -10393,7 +10393,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3485</t>
+          <t>3473</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1124</t>
+          <t>1233</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5616</t>
+          <t>5507</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>53,97%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10458,12 +10458,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7420</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10473,12 +10473,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>35,66%</t>
         </is>
       </c>
     </row>
@@ -10506,7 +10506,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4266</t>
+          <t>3559</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10521,7 +10521,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3932</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10571,12 +10571,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>648</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5815</t>
+          <t>6036</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>30,39%</t>
         </is>
       </c>
     </row>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4515</t>
+          <t>4717</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10634,7 +10634,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10649,12 +10649,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>573</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4813</t>
+          <t>4228</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10664,12 +10664,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10684,12 +10684,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6980</t>
+          <t>6997</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10699,12 +10699,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,23%</t>
         </is>
       </c>
     </row>
@@ -10727,7 +10727,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3106</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -10762,12 +10762,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>590</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4161</t>
+          <t>4785</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10777,12 +10777,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10797,12 +10797,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4346</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11647</t>
+          <t>11268</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>56,74%</t>
         </is>
       </c>
     </row>
@@ -11301,7 +11301,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3683</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11316,7 +11316,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4681</t>
+          <t>4034</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11351,7 +11351,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11366,12 +11366,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>656</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5497</t>
+          <t>5368</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11381,12 +11381,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,43%</t>
         </is>
       </c>
     </row>
@@ -11409,12 +11409,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>4058</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9384</t>
+          <t>9290</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11424,12 +11424,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11444,12 +11444,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3991</t>
+          <t>4588</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10193</t>
+          <t>10190</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11459,12 +11459,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10093</t>
+          <t>10594</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>18439</t>
+          <t>17984</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11494,12 +11494,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>71,79%</t>
         </is>
       </c>
     </row>
@@ -11527,7 +11527,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3888</t>
+          <t>4497</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11542,7 +11542,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11557,12 +11557,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1421</t>
+          <t>760</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6430</t>
+          <t>6400</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11572,12 +11572,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11592,12 +11592,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2199</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9443</t>
+          <t>8807</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11607,12 +11607,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>35,16%</t>
         </is>
       </c>
     </row>
@@ -11635,12 +11635,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>643</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4812</t>
+          <t>4973</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11650,12 +11650,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11675,7 +11675,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4424</t>
+          <t>4372</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11705,12 +11705,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7044</t>
+          <t>7236</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11720,12 +11720,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,89%</t>
         </is>
       </c>
     </row>
@@ -11940,7 +11940,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4490</t>
+          <t>4332</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>59,2%</t>
         </is>
       </c>
     </row>
@@ -12209,7 +12209,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2726</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -12224,7 +12224,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -12279,7 +12279,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3025</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -12294,7 +12294,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>40,85%</t>
         </is>
       </c>
     </row>
@@ -12392,7 +12392,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4481</t>
+          <t>4317</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12407,7 +12407,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>58,99%</t>
         </is>
       </c>
     </row>
@@ -12435,7 +12435,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>2570</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12450,7 +12450,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12505,7 +12505,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3433</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12520,7 +12520,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>46,54%</t>
         </is>
       </c>
     </row>
@@ -12548,7 +12548,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2726</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12563,7 +12563,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12583,7 +12583,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4593</t>
+          <t>3958</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12598,7 +12598,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12613,12 +12613,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>632</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5413</t>
+          <t>5608</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12628,12 +12628,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>76,63%</t>
         </is>
       </c>
     </row>
@@ -12961,7 +12961,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2994</t>
+          <t>2903</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -12976,7 +12976,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>71,46%</t>
         </is>
       </c>
     </row>
@@ -13300,7 +13300,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2660</t>
+          <t>2662</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -13315,7 +13315,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>65,52%</t>
         </is>
       </c>
     </row>
@@ -13413,7 +13413,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2651</t>
+          <t>2641</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -13428,7 +13428,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>65,0%</t>
         </is>
       </c>
     </row>
@@ -13521,12 +13521,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>677</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3419</t>
+          <t>3416</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -13536,12 +13536,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,09%</t>
         </is>
       </c>
     </row>
@@ -14025,7 +14025,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>4300</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -14040,7 +14040,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>54,58%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>4008</t>
+          <t>3762</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -14110,7 +14110,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>
@@ -14133,12 +14133,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>5951</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -14148,12 +14148,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -14168,12 +14168,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3525</t>
+          <t>3432</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>9431</t>
+          <t>9486</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -14183,12 +14183,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -14203,12 +14203,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>6366</t>
+          <t>6217</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>14198</t>
+          <t>13954</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -14218,12 +14218,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>66,35%</t>
         </is>
       </c>
     </row>
@@ -14246,12 +14246,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>845</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>5666</t>
+          <t>5724</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -14261,12 +14261,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -14281,12 +14281,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>7235</t>
+          <t>7614</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -14296,12 +14296,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -14316,12 +14316,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>3674</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>11090</t>
+          <t>10726</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -14331,12 +14331,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>51,0%</t>
         </is>
       </c>
     </row>
@@ -14364,7 +14364,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2197</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -14379,7 +14379,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -14394,12 +14394,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>765</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>6348</t>
+          <t>6211</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -14409,12 +14409,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -14429,12 +14429,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>794</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>6953</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -14444,12 +14444,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,06%</t>
         </is>
       </c>
     </row>
@@ -14629,7 +14629,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>2857</t>
+          <t>2866</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -14664,7 +14664,7 @@
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>3039</t>
+          <t>2844</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -14679,7 +14679,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -14968,7 +14968,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>3168</t>
+          <t>3299</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -14983,7 +14983,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -15003,7 +15003,7 @@
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>3733</t>
+          <t>3325</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -15018,7 +15018,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -15041,12 +15041,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>4192</t>
+          <t>4292</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>9849</t>
+          <t>9901</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -15056,12 +15056,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -15076,12 +15076,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>5441</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>12792</t>
+          <t>12553</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -15111,12 +15111,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>11823</t>
+          <t>10997</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>21239</t>
+          <t>20561</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -15126,12 +15126,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>63,4%</t>
         </is>
       </c>
     </row>
@@ -15154,12 +15154,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>6972</t>
+          <t>7055</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -15169,12 +15169,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -15189,12 +15189,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>7494</t>
+          <t>7583</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -15204,12 +15204,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -15224,12 +15224,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>4201</t>
+          <t>4176</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>12253</t>
+          <t>11918</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -15239,12 +15239,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>36,75%</t>
         </is>
       </c>
     </row>
@@ -15272,7 +15272,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>2703</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -15287,7 +15287,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -15302,12 +15302,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>2939</t>
+          <t>3346</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>9780</t>
+          <t>10041</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -15317,12 +15317,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -15337,12 +15337,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>3972</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>11322</t>
+          <t>11279</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -15352,12 +15352,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,78%</t>
         </is>
       </c>
     </row>
@@ -15836,12 +15836,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>629</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>4504</t>
+          <t>4454</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -15851,12 +15851,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -15906,12 +15906,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>743</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>5277</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -15921,12 +15921,12 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>56,04%</t>
         </is>
       </c>
     </row>
@@ -15954,7 +15954,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2934</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -15969,7 +15969,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>639</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>3455</t>
+          <t>3448</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -15999,12 +15999,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -16019,12 +16019,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>701</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>5281</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -16034,12 +16034,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>54,56%</t>
         </is>
       </c>
     </row>
@@ -16067,7 +16067,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2514</t>
+          <t>2726</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -16082,7 +16082,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -16117,7 +16117,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -16132,12 +16132,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>579</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>4418</t>
+          <t>4428</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -16147,12 +16147,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>45,75%</t>
         </is>
       </c>
     </row>
@@ -16175,12 +16175,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>3722</t>
+          <t>3731</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -16190,12 +16190,12 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>66,4%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -16215,7 +16215,7 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>2832</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -16230,7 +16230,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -16245,12 +16245,12 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>627</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>5137</t>
+          <t>5187</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -16260,12 +16260,12 @@
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>53,58%</t>
         </is>
       </c>
     </row>
@@ -16410,7 +16410,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>3346</t>
+          <t>3028</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -16425,7 +16425,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -16445,7 +16445,7 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>5572</t>
+          <t>6348</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -16460,7 +16460,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -16475,12 +16475,12 @@
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>659</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>6214</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
@@ -16490,12 +16490,12 @@
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -16523,7 +16523,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>4254</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -16538,7 +16538,7 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -16558,7 +16558,7 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>6627</t>
+          <t>7074</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -16573,7 +16573,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -16588,12 +16588,12 @@
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>645</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>8253</t>
+          <t>8075</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
@@ -16608,7 +16608,7 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>2758</t>
+          <t>3197</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -16686,7 +16686,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -16706,7 +16706,7 @@
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>2834</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
@@ -16721,7 +16721,7 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -16744,12 +16744,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>2595</t>
+          <t>2664</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>9667</t>
+          <t>10309</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -16759,12 +16759,12 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -16779,12 +16779,12 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3239</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>10823</t>
+          <t>11003</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -16794,12 +16794,12 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -16814,12 +16814,12 @@
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>7377</t>
+          <t>7027</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>18061</t>
+          <t>18003</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -16829,12 +16829,12 @@
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -16857,12 +16857,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>14360</t>
+          <t>14332</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>25750</t>
+          <t>25645</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -16872,12 +16872,12 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -16892,12 +16892,12 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>24817</t>
+          <t>24048</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>38729</t>
+          <t>38589</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -16907,12 +16907,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -16927,12 +16927,12 @@
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>42587</t>
+          <t>42556</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>61194</t>
+          <t>60190</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -16942,12 +16942,12 @@
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>48,12%</t>
         </is>
       </c>
     </row>
@@ -16970,12 +16970,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>7250</t>
+          <t>6751</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>17076</t>
+          <t>16947</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -16985,12 +16985,12 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -17005,12 +17005,12 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>9451</t>
+          <t>9873</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>21168</t>
+          <t>21011</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -17020,12 +17020,12 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -17040,12 +17040,12 @@
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>19871</t>
+          <t>19705</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>35020</t>
+          <t>35053</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,02%</t>
         </is>
       </c>
     </row>
@@ -17083,12 +17083,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>8847</t>
+          <t>8693</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>19169</t>
+          <t>18805</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -17098,12 +17098,12 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -17118,12 +17118,12 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>10829</t>
+          <t>11059</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>23081</t>
+          <t>22917</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -17133,12 +17133,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -17153,12 +17153,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>22309</t>
+          <t>22143</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>37482</t>
+          <t>37987</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -17168,12 +17168,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,37%</t>
         </is>
       </c>
     </row>
@@ -17850,7 +17850,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2960</t>
+          <t>2999</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -17865,7 +17865,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>35,1%</t>
         </is>
       </c>
     </row>
@@ -17923,12 +17923,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>1124</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5419</t>
+          <t>5209</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -17938,12 +17938,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -17958,12 +17958,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>1662</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6665</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -17973,12 +17973,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>78,29%</t>
         </is>
       </c>
     </row>
@@ -18036,12 +18036,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>956</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4970</t>
+          <t>5041</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -18051,12 +18051,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -18071,12 +18071,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>587</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5096</t>
+          <t>5207</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -18086,12 +18086,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>60,94%</t>
         </is>
       </c>
     </row>
@@ -18189,7 +18189,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3234</t>
+          <t>3216</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -18204,7 +18204,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,63%</t>
         </is>
       </c>
     </row>
@@ -18302,7 +18302,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3027</t>
+          <t>2627</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -18317,7 +18317,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>30,74%</t>
         </is>
       </c>
     </row>
@@ -18703,7 +18703,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -18758,7 +18758,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3164</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -18773,7 +18773,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>29,44%</t>
         </is>
       </c>
     </row>
@@ -18836,7 +18836,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>3509</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -18851,7 +18851,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -18871,7 +18871,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4173</t>
+          <t>4192</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -18886,7 +18886,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,49%</t>
         </is>
       </c>
     </row>
@@ -18914,7 +18914,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2798</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -18929,7 +18929,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -18944,12 +18944,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>685</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>4182</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -18979,12 +18979,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>711</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5503</t>
+          <t>5648</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -18994,12 +18994,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>46,46%</t>
         </is>
       </c>
     </row>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4688</t>
+          <t>4696</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -19037,12 +19037,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -19062,7 +19062,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3318</t>
+          <t>3920</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -19077,7 +19077,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -19092,12 +19092,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7859</t>
+          <t>7366</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -19107,12 +19107,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>60,6%</t>
         </is>
       </c>
     </row>
@@ -19140,7 +19140,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3289</t>
+          <t>3247</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -19155,7 +19155,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -19170,12 +19170,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>630</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4682</t>
+          <t>4662</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -19205,12 +19205,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5990</t>
+          <t>5463</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -19220,12 +19220,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>44,95%</t>
         </is>
       </c>
     </row>
@@ -20278,7 +20278,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>2708</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -20293,7 +20293,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -20348,7 +20348,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2969</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -20363,7 +20363,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -20617,7 +20617,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2983</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -20632,7 +20632,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -20647,12 +20647,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>719</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5173</t>
+          <t>4559</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -20662,12 +20662,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -20682,12 +20682,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>764</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6007</t>
+          <t>6261</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -20697,12 +20697,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>48,99%</t>
         </is>
       </c>
     </row>
@@ -20730,7 +20730,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3368</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -20745,7 +20745,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -20760,12 +20760,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5796</t>
+          <t>5758</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -20775,12 +20775,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -20795,12 +20795,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2083</t>
+          <t>1948</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>8008</t>
+          <t>7835</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -20810,12 +20810,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>61,31%</t>
         </is>
       </c>
     </row>
@@ -20843,7 +20843,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3530</t>
+          <t>3517</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -20858,7 +20858,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -20878,7 +20878,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>2823</t>
+          <t>4099</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -20893,7 +20893,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -20913,7 +20913,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>5397</t>
+          <t>5325</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -20928,7 +20928,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>41,67%</t>
         </is>
       </c>
     </row>
@@ -20956,7 +20956,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3746</t>
+          <t>3660</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -20971,7 +20971,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -20991,7 +20991,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4141</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -21006,7 +21006,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -21021,12 +21021,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>707</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6235</t>
+          <t>5957</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -21036,12 +21036,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>46,61%</t>
         </is>
       </c>
     </row>
@@ -22390,7 +22390,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>3247</t>
+          <t>3323</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -22405,7 +22405,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,91%</t>
         </is>
       </c>
     </row>
@@ -22468,7 +22468,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>3820</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -22483,7 +22483,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -22503,7 +22503,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>4325</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -22518,7 +22518,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>55,74%</t>
         </is>
       </c>
     </row>
@@ -22581,7 +22581,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3687</t>
+          <t>3710</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -22596,7 +22596,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -22611,12 +22611,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>731</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>5399</t>
+          <t>5762</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -22626,12 +22626,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>60,54%</t>
         </is>
       </c>
     </row>
@@ -22659,7 +22659,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2836</t>
+          <t>2913</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -22674,7 +22674,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3880</t>
+          <t>3910</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -22709,7 +22709,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -22724,12 +22724,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>746</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>5339</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -22739,12 +22739,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>56,09%</t>
         </is>
       </c>
     </row>
@@ -22807,7 +22807,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3621</t>
+          <t>3751</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -22822,7 +22822,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -22837,12 +22837,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>668</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>4935</t>
+          <t>4379</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -22852,12 +22852,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>46,0%</t>
         </is>
       </c>
     </row>
@@ -23263,7 +23263,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>2767</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -23278,7 +23278,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -23298,7 +23298,7 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>3899</t>
+          <t>3646</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -23313,7 +23313,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>55,42%</t>
         </is>
       </c>
     </row>
@@ -23341,7 +23341,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>2663</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -23356,7 +23356,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -23371,7 +23371,7 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>540</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -23386,7 +23386,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -23406,12 +23406,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>595</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>4537</t>
+          <t>4447</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -23421,12 +23421,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>67,61%</t>
         </is>
       </c>
     </row>
@@ -23454,7 +23454,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>2663</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -23469,7 +23469,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -23524,7 +23524,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>2822</t>
+          <t>2855</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -23539,7 +23539,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>43,4%</t>
         </is>
       </c>
     </row>
@@ -23567,7 +23567,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>2111</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -23582,7 +23582,7 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -23602,7 +23602,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -23617,7 +23617,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -23632,12 +23632,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>618</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>4464</t>
+          <t>4593</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -23647,12 +23647,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>69,82%</t>
         </is>
       </c>
     </row>
@@ -23910,7 +23910,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2093</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -23925,7 +23925,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>63,63%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -23945,7 +23945,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>2631</t>
+          <t>3609</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -23960,7 +23960,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -23980,7 +23980,7 @@
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>3235</t>
+          <t>3266</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -23995,7 +23995,7 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,52%</t>
         </is>
       </c>
     </row>
@@ -24171,7 +24171,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>2518</t>
+          <t>2525</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -24186,7 +24186,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -24206,7 +24206,7 @@
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>3235</t>
+          <t>3842</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -24221,7 +24221,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>37,08%</t>
         </is>
       </c>
     </row>
@@ -24249,7 +24249,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>2656</t>
+          <t>2592</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -24264,7 +24264,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -24284,7 +24284,7 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>2799</t>
+          <t>2947</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -24299,7 +24299,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -24314,12 +24314,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>515</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>4509</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -24329,12 +24329,12 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>43,51%</t>
         </is>
       </c>
     </row>
@@ -24362,7 +24362,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -24377,7 +24377,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -24397,7 +24397,7 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>4067</t>
+          <t>3488</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -24412,7 +24412,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -24432,7 +24432,7 @@
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>4177</t>
+          <t>3935</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -24447,7 +24447,7 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>37,97%</t>
         </is>
       </c>
     </row>
@@ -24475,7 +24475,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2211</t>
+          <t>2205</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -24490,7 +24490,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -24505,12 +24505,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>761</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>4992</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -24520,12 +24520,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -24540,12 +24540,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>6025</t>
+          <t>6017</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -24555,12 +24555,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>58,07%</t>
         </is>
       </c>
     </row>
@@ -24588,7 +24588,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2067</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -24603,7 +24603,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -24618,12 +24618,12 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>526</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>3918</t>
+          <t>3825</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -24633,12 +24633,12 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -24653,12 +24653,12 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>568</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>4689</t>
+          <t>4727</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -24668,12 +24668,12 @@
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>45,61%</t>
         </is>
       </c>
     </row>
@@ -24818,7 +24818,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>3277</t>
+          <t>3151</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -24833,7 +24833,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -24853,7 +24853,7 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>3882</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -24868,7 +24868,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -24883,12 +24883,12 @@
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>567</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>5796</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
@@ -24898,12 +24898,12 @@
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -25039,12 +25039,12 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>765</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>6041</t>
+          <t>6280</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -25054,12 +25054,12 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -25079,7 +25079,7 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>4445</t>
+          <t>4041</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -25094,7 +25094,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -25109,12 +25109,12 @@
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>1494</t>
+          <t>1426</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>8151</t>
+          <t>7423</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
@@ -25124,12 +25124,12 @@
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -25152,12 +25152,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>6738</t>
+          <t>6594</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -25167,12 +25167,12 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -25187,12 +25187,12 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>7752</t>
+          <t>7605</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>17264</t>
+          <t>17704</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -25202,12 +25202,12 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -25222,12 +25222,12 @@
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>10407</t>
+          <t>10554</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>22582</t>
+          <t>22180</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -25237,12 +25237,12 @@
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>34,61%</t>
         </is>
       </c>
     </row>
@@ -25265,12 +25265,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>8520</t>
+          <t>8286</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -25280,12 +25280,12 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -25300,12 +25300,12 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>6564</t>
+          <t>6641</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>15971</t>
+          <t>15963</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -25315,12 +25315,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -25335,12 +25335,12 @@
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>10648</t>
+          <t>10210</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>22108</t>
+          <t>21415</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -25350,12 +25350,12 @@
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>33,41%</t>
         </is>
       </c>
     </row>
@@ -25378,12 +25378,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>4496</t>
+          <t>4370</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>12198</t>
+          <t>11996</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -25393,12 +25393,12 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -25413,12 +25413,12 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>4266</t>
+          <t>4138</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>12623</t>
+          <t>12668</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -25428,12 +25428,12 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -25448,12 +25448,12 @@
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>10548</t>
+          <t>10385</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>21424</t>
+          <t>21838</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -25463,12 +25463,12 @@
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>34,07%</t>
         </is>
       </c>
     </row>
@@ -25491,12 +25491,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>1523</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>7537</t>
+          <t>7300</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -25506,12 +25506,12 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -25526,12 +25526,12 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>3878</t>
+          <t>3926</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>11573</t>
+          <t>11848</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -25541,12 +25541,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -25561,12 +25561,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>6722</t>
+          <t>6586</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>16139</t>
+          <t>16515</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -25576,12 +25576,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,77%</t>
         </is>
       </c>
     </row>
@@ -26258,7 +26258,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3660</t>
+          <t>3769</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -26273,7 +26273,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>54,24%</t>
         </is>
       </c>
     </row>
@@ -26371,7 +26371,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5195</t>
+          <t>5341</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -26386,7 +26386,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>76,86%</t>
         </is>
       </c>
     </row>
@@ -26592,12 +26592,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>665</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6065</t>
+          <t>5644</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -26607,12 +26607,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>81,22%</t>
         </is>
       </c>
     </row>
@@ -26710,7 +26710,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4711</t>
+          <t>4620</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -26725,7 +26725,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>66,48%</t>
         </is>
       </c>
     </row>
@@ -27131,7 +27131,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4157</t>
+          <t>4143</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -27146,7 +27146,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -27166,7 +27166,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4969</t>
+          <t>4729</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -27181,7 +27181,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>58,97%</t>
         </is>
       </c>
     </row>
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2292</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -27259,7 +27259,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -27279,7 +27279,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>3367</t>
+          <t>4147</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -27294,7 +27294,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>51,7%</t>
         </is>
       </c>
     </row>
@@ -27357,7 +27357,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4488</t>
+          <t>4271</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -27372,7 +27372,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -27387,12 +27387,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>795</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5544</t>
+          <t>5441</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -27402,12 +27402,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>67,85%</t>
         </is>
       </c>
     </row>
@@ -27505,7 +27505,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3793</t>
+          <t>2971</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -27520,7 +27520,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>37,05%</t>
         </is>
       </c>
     </row>
@@ -27583,7 +27583,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3601</t>
+          <t>3498</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -27598,7 +27598,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -27618,7 +27618,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4580</t>
+          <t>4405</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -27633,7 +27633,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>54,92%</t>
         </is>
       </c>
     </row>
@@ -28074,7 +28074,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2430</t>
+          <t>2619</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -28089,7 +28089,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>68,18%</t>
         </is>
       </c>
     </row>
@@ -28187,7 +28187,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2911</t>
+          <t>2924</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -28202,7 +28202,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>76,11%</t>
         </is>
       </c>
     </row>
@@ -28295,12 +28295,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>365</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3197</t>
+          <t>3224</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -28310,12 +28310,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,94%</t>
         </is>
       </c>
     </row>
@@ -28526,7 +28526,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>2487</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -28541,7 +28541,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>64,74%</t>
         </is>
       </c>
     </row>
@@ -30841,7 +30841,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2369</t>
+          <t>2166</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -30856,7 +30856,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -30911,7 +30911,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>2423</t>
+          <t>2806</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -30926,7 +30926,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>48,52%</t>
         </is>
       </c>
     </row>
@@ -30954,7 +30954,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2689</t>
+          <t>2827</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -30969,7 +30969,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -31019,12 +31019,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>1356</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>5071</t>
+          <t>5127</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -31034,12 +31034,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>88,65%</t>
         </is>
       </c>
     </row>
@@ -31067,7 +31067,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2573</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -31082,7 +31082,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -31137,7 +31137,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>2742</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -31152,7 +31152,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>55,52%</t>
         </is>
       </c>
     </row>
@@ -31180,7 +31180,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2790</t>
+          <t>2578</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -31195,7 +31195,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -31250,7 +31250,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>3562</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -31265,7 +31265,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>61,02%</t>
         </is>
       </c>
     </row>
@@ -31410,7 +31410,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>2071</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -31425,7 +31425,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -31480,7 +31480,7 @@
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>2485</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -31495,7 +31495,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>22,93%</t>
         </is>
       </c>
     </row>
@@ -31784,7 +31784,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>2981</t>
+          <t>3396</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -31799,7 +31799,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>49,67%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -31819,7 +31819,7 @@
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>3066</t>
+          <t>3313</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -31834,7 +31834,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>30,56%</t>
         </is>
       </c>
     </row>
@@ -31857,12 +31857,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>355</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>3382</t>
+          <t>3477</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -31872,12 +31872,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -31892,12 +31892,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>5973</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -31907,12 +31907,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -31927,12 +31927,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>2707</t>
+          <t>2388</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>7948</t>
+          <t>7630</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -31942,12 +31942,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>70,39%</t>
         </is>
       </c>
     </row>
@@ -31970,12 +31970,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>440</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>3586</t>
+          <t>3580</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -31985,12 +31985,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -32010,7 +32010,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>4501</t>
+          <t>4046</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -32025,7 +32025,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -32040,12 +32040,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>1338</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>6160</t>
+          <t>6597</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -32055,12 +32055,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>60,85%</t>
         </is>
       </c>
     </row>
@@ -32123,7 +32123,7 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>3772</t>
+          <t>4143</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -32138,7 +32138,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -32158,7 +32158,7 @@
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>3648</t>
+          <t>3954</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -32173,7 +32173,7 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>36,47%</t>
         </is>
       </c>
     </row>
@@ -33226,7 +33226,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>2288</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -33241,7 +33241,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -33296,7 +33296,7 @@
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>2233</t>
+          <t>2338</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
@@ -33311,7 +33311,7 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -33452,7 +33452,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>4094</t>
+          <t>4444</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -33467,7 +33467,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -33487,7 +33487,7 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>5429</t>
+          <t>5821</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -33502,7 +33502,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -33517,12 +33517,12 @@
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>7497</t>
+          <t>7244</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
@@ -33532,12 +33532,12 @@
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,59%</t>
         </is>
       </c>
     </row>
@@ -33560,12 +33560,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>7310</t>
+          <t>7051</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -33575,12 +33575,12 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -33595,12 +33595,12 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>1106</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>9095</t>
+          <t>9221</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -33610,12 +33610,12 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -33630,12 +33630,12 @@
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>3628</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>14477</t>
+          <t>13957</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -33645,12 +33645,12 @@
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>33,89%</t>
         </is>
       </c>
     </row>
@@ -33673,12 +33673,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>7345</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -33688,12 +33688,12 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -33708,12 +33708,12 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>6380</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>15035</t>
+          <t>15172</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -33723,12 +33723,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -33743,12 +33743,12 @@
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>9280</t>
+          <t>9612</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>19717</t>
+          <t>19990</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -33758,12 +33758,12 @@
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>48,54%</t>
         </is>
       </c>
     </row>
@@ -33786,12 +33786,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>9148</t>
+          <t>9481</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -33801,12 +33801,12 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -33821,12 +33821,12 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1421</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>8696</t>
+          <t>8543</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -33836,12 +33836,12 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -33856,12 +33856,12 @@
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>5492</t>
+          <t>5663</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>15461</t>
+          <t>16116</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -33871,12 +33871,12 @@
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>39,13%</t>
         </is>
       </c>
     </row>
@@ -33899,12 +33899,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>380</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>5782</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -33914,12 +33914,12 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -33934,12 +33934,12 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>8526</t>
+          <t>8660</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -33949,12 +33949,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -33969,12 +33969,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>2479</t>
+          <t>2430</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>10864</t>
+          <t>10889</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -33984,12 +33984,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,44%</t>
         </is>
       </c>
     </row>
